--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260922.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260922.xlsx
@@ -695,7 +695,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1713,7 +1713,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2367,7 +2367,7 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2593,7 +2593,7 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13981,7 +13981,7 @@
       <c r="AD118" t="inlineStr"/>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15819,7 +15819,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16625,7 +16625,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18707,7 +18707,7 @@
       <c r="AD159" t="inlineStr"/>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19325,7 +19325,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19447,7 +19447,7 @@
       <c r="AD165" t="inlineStr"/>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19885,7 +19885,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20353,7 +20353,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20467,7 +20467,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20581,7 +20581,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20915,7 +20915,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21143,7 +21143,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21371,7 +21371,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21721,7 +21721,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21841,7 +21841,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21963,7 +21963,7 @@
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -22089,7 +22089,7 @@
       <c r="AD188" t="inlineStr"/>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22215,7 +22215,7 @@
       <c r="AD189" t="inlineStr"/>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22793,7 +22793,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22913,7 +22913,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23243,7 +23243,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23599,7 +23599,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -24049,7 +24049,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24271,7 +24271,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24507,7 +24507,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24975,7 +24975,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25087,7 +25087,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25313,7 +25313,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25433,7 +25433,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25543,7 +25543,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25887,7 +25887,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25997,7 +25997,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26553,7 +26553,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26785,7 +26785,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26895,7 +26895,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -27019,7 +27019,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27143,7 +27143,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27473,7 +27473,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27585,7 +27585,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27695,7 +27695,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27805,7 +27805,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27933,7 +27933,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -28039,7 +28039,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28267,7 +28267,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28383,7 +28383,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28493,7 +28493,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28603,7 +28603,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28835,7 +28835,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29061,7 +29061,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29177,7 +29177,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29287,7 +29287,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29507,7 +29507,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29723,7 +29723,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29945,7 +29945,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30055,7 +30055,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30175,7 +30175,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30287,7 +30287,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30397,7 +30397,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30509,7 +30509,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30625,7 +30625,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30847,7 +30847,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31073,7 +31073,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31199,7 +31199,7 @@
       <c r="AD268" t="inlineStr"/>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31327,7 +31327,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31539,7 +31539,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31639,7 +31639,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31753,7 +31753,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31867,7 +31867,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31967,7 +31967,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32087,7 +32087,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32199,7 +32199,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32311,7 +32311,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32425,7 +32425,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32539,7 +32539,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32653,7 +32653,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32785,7 +32785,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -33041,7 +33041,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33281,7 +33281,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33393,7 +33393,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33503,7 +33503,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33613,7 +33613,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33741,7 +33741,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33851,7 +33851,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33979,7 +33979,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34091,7 +34091,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34203,7 +34203,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34313,7 +34313,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34433,7 +34433,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34557,7 +34557,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34681,7 +34681,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34805,7 +34805,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -35033,7 +35033,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35273,7 +35273,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35401,7 +35401,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35513,7 +35513,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35625,7 +35625,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35735,7 +35735,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35845,7 +35845,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35961,7 +35961,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36073,7 +36073,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36193,7 +36193,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36437,7 +36437,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36537,7 +36537,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36649,7 +36649,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36777,7 +36777,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36901,7 +36901,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -37013,7 +37013,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37123,7 +37123,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37233,7 +37233,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37343,7 +37343,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37453,7 +37453,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37573,7 +37573,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37683,7 +37683,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37793,7 +37793,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -38023,7 +38023,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38143,7 +38143,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38263,7 +38263,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38383,7 +38383,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38615,7 +38615,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38731,7 +38731,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38843,7 +38843,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38959,7 +38959,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39079,7 +39079,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39307,7 +39307,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39423,7 +39423,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39539,7 +39539,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39655,7 +39655,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39769,7 +39769,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:18</t>
+          <t>2026-09-22 13:36:50</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39885,7 +39885,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -40001,7 +40001,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40117,7 +40117,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40227,7 +40227,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40343,7 +40343,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40455,7 +40455,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40565,7 +40565,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40677,7 +40677,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40789,7 +40789,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40901,7 +40901,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -41021,7 +41021,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41149,7 +41149,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41269,7 +41269,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41397,7 +41397,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41509,7 +41509,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41619,7 +41619,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41841,7 +41841,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41953,7 +41953,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42063,7 +42063,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42179,7 +42179,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42289,7 +42289,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42401,7 +42401,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42511,7 +42511,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42621,7 +42621,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42749,7 +42749,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42989,7 +42989,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43101,7 +43101,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43211,7 +43211,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43321,7 +43321,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43431,7 +43431,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43543,7 +43543,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43653,7 +43653,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43781,7 +43781,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43893,7 +43893,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -44003,7 +44003,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44113,7 +44113,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44223,7 +44223,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44333,7 +44333,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44443,7 +44443,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44555,7 +44555,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44683,7 +44683,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44793,7 +44793,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44903,7 +44903,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -45015,7 +45015,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45125,7 +45125,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45237,7 +45237,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45365,7 +45365,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45475,7 +45475,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45587,7 +45587,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45697,7 +45697,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45807,7 +45807,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45917,7 +45917,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -46017,7 +46017,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46127,7 +46127,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46227,7 +46227,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46337,7 +46337,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46465,7 +46465,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46575,7 +46575,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46685,7 +46685,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46795,7 +46795,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46905,7 +46905,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -47015,7 +47015,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47125,7 +47125,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47235,7 +47235,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47345,7 +47345,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47473,7 +47473,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47585,7 +47585,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47685,7 +47685,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47795,7 +47795,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47909,7 +47909,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -48019,7 +48019,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48119,7 +48119,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48231,7 +48231,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48343,7 +48343,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48453,7 +48453,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48565,7 +48565,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48677,7 +48677,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48787,7 +48787,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48915,7 +48915,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -49047,7 +49047,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49179,7 +49179,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49311,7 +49311,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49435,7 +49435,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49547,7 +49547,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49767,7 +49767,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49883,7 +49883,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49995,7 +49995,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50117,7 +50117,7 @@
       <c r="AD433" t="inlineStr"/>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50229,7 +50229,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50339,7 +50339,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50449,7 +50449,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50559,7 +50559,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50669,7 +50669,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50797,7 +50797,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50913,7 +50913,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -51023,7 +51023,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51151,7 +51151,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51279,7 +51279,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51407,7 +51407,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51647,7 +51647,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51757,7 +51757,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51885,7 +51885,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51997,7 +51997,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52109,7 +52109,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52225,7 +52225,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52337,7 +52337,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52449,7 +52449,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52561,7 +52561,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52673,7 +52673,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52793,7 +52793,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52903,7 +52903,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -53031,7 +53031,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53151,7 +53151,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53263,7 +53263,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53375,7 +53375,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53475,7 +53475,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53591,7 +53591,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53701,7 +53701,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53813,7 +53813,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53923,7 +53923,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -54035,7 +54035,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54147,7 +54147,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54247,7 +54247,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54357,7 +54357,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54469,7 +54469,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54579,7 +54579,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54689,7 +54689,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54801,7 +54801,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54911,7 +54911,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -55021,7 +55021,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55131,7 +55131,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55251,7 +55251,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55375,7 +55375,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:20</t>
+          <t>2026-09-22 13:36:52</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55485,7 +55485,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55597,7 +55597,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55707,7 +55707,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55819,7 +55819,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55931,7 +55931,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -56041,7 +56041,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56151,7 +56151,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56261,7 +56261,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56371,7 +56371,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56481,7 +56481,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56591,7 +56591,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56703,7 +56703,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56815,7 +56815,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56927,7 +56927,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -57037,7 +57037,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57149,7 +57149,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57249,7 +57249,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57359,7 +57359,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57459,7 +57459,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57559,7 +57559,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57671,7 +57671,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57783,7 +57783,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57895,7 +57895,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -58005,7 +58005,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58225,7 +58225,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58337,7 +58337,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58447,7 +58447,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58557,7 +58557,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58667,7 +58667,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58777,7 +58777,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58889,7 +58889,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -59001,7 +59001,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59117,7 +59117,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59245,7 +59245,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59357,7 +59357,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59467,7 +59467,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59587,7 +59587,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59697,7 +59697,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59807,7 +59807,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59917,7 +59917,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60037,7 +60037,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60153,7 +60153,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60265,7 +60265,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60385,7 +60385,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60497,7 +60497,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60597,7 +60597,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60717,7 +60717,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60827,7 +60827,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60939,7 +60939,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61055,7 +61055,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61167,7 +61167,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61279,7 +61279,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61407,7 +61407,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61517,7 +61517,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61627,7 +61627,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61737,7 +61737,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61849,7 +61849,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61977,7 +61977,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62089,7 +62089,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62201,7 +62201,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62313,7 +62313,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62413,7 +62413,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62523,7 +62523,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62633,7 +62633,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62733,7 +62733,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62843,7 +62843,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62971,7 +62971,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63081,7 +63081,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63193,7 +63193,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63303,7 +63303,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63415,7 +63415,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63525,7 +63525,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63635,7 +63635,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63735,7 +63735,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63845,7 +63845,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63957,7 +63957,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64067,7 +64067,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64177,7 +64177,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64287,7 +64287,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64397,7 +64397,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64507,7 +64507,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64617,7 +64617,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64717,7 +64717,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64827,7 +64827,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64937,7 +64937,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65049,7 +65049,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65159,7 +65159,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65271,7 +65271,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65381,7 +65381,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65491,7 +65491,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65601,7 +65601,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65711,7 +65711,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65821,7 +65821,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65933,7 +65933,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66043,7 +66043,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66155,7 +66155,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66267,7 +66267,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66377,7 +66377,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66489,7 +66489,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66601,7 +66601,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66711,7 +66711,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66821,7 +66821,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66931,7 +66931,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67041,7 +67041,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67141,7 +67141,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67253,7 +67253,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67363,7 +67363,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67473,7 +67473,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67601,7 +67601,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67713,7 +67713,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67825,7 +67825,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67953,7 +67953,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68065,7 +68065,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68193,7 +68193,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68321,7 +68321,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:08</t>
+          <t>2026-09-22 13:36:40</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68433,7 +68433,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68545,7 +68545,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68655,7 +68655,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68767,7 +68767,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68877,7 +68877,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68987,7 +68987,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69099,7 +69099,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69211,7 +69211,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69323,7 +69323,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69433,7 +69433,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69543,7 +69543,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69655,7 +69655,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69767,7 +69767,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69877,7 +69877,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69989,7 +69989,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70099,7 +70099,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70199,7 +70199,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70309,7 +70309,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70421,7 +70421,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70531,7 +70531,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70643,7 +70643,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70753,7 +70753,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70863,7 +70863,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70973,7 +70973,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71083,7 +71083,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71193,7 +71193,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71305,7 +71305,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71415,7 +71415,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71525,7 +71525,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71635,7 +71635,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71747,7 +71747,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71857,7 +71857,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71969,7 +71969,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72081,7 +72081,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72181,7 +72181,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72291,7 +72291,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72403,7 +72403,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72515,7 +72515,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72627,7 +72627,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72739,7 +72739,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72849,7 +72849,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72959,7 +72959,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73071,7 +73071,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73181,7 +73181,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73293,7 +73293,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73393,7 +73393,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73503,7 +73503,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73615,7 +73615,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73725,7 +73725,7 @@
       <c r="AD644" t="inlineStr"/>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:33</t>
+          <t>2026-09-22 13:37:05</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73837,7 +73837,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73949,7 +73949,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74059,7 +74059,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74171,7 +74171,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74271,7 +74271,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74371,7 +74371,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74471,7 +74471,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74583,7 +74583,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74683,7 +74683,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74793,7 +74793,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74893,7 +74893,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -75005,7 +75005,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75117,7 +75117,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75229,7 +75229,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75341,7 +75341,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75441,7 +75441,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75553,7 +75553,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75663,7 +75663,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75775,7 +75775,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75875,7 +75875,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75975,7 +75975,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76075,7 +76075,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76175,7 +76175,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76287,7 +76287,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76399,7 +76399,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76499,7 +76499,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76609,7 +76609,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76721,7 +76721,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76833,7 +76833,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76945,7 +76945,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77057,7 +77057,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77169,7 +77169,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77281,7 +77281,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77393,7 +77393,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77493,7 +77493,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77593,7 +77593,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77705,7 +77705,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:02</t>
+          <t>2026-09-22 13:36:33</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77805,7 +77805,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77905,7 +77905,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78005,7 +78005,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78115,7 +78115,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78215,7 +78215,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78325,7 +78325,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78407,7 +78407,7 @@
       <c r="AD688" t="inlineStr"/>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78489,7 +78489,7 @@
       <c r="AD689" t="inlineStr"/>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78571,7 +78571,7 @@
       <c r="AD690" t="inlineStr"/>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78653,7 +78653,7 @@
       <c r="AD691" t="inlineStr"/>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
